--- a/activity/M03A02/M03A02_VerificacionTopologia.xlsx
+++ b/activity/M03A02/M03A02_VerificacionTopologia.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28403"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebacorreoescuelaingeduco-my.sharepoint.com/personal/william_aguilar_escuelaing_edu_co/Documents/UECIJG.Student/HCMC2024.2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="799" documentId="13_ncr:1_{9E9C72E5-8AD7-4C1E-9154-AAA880FF6C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23A7F953-61CF-4DAF-BFAD-747BEF6A73A5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD59455-5145-42D5-B58A-377D41D7A8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="7973" windowWidth="28996" windowHeight="16395" tabRatio="630" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="630" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
     <sheet name="Detalle" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Detalle!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="34">
   <si>
     <t>Observaciones</t>
   </si>
@@ -50,16 +50,10 @@
     <t>Código</t>
   </si>
   <si>
-    <t>Promedio</t>
-  </si>
-  <si>
     <t>Requerimiento</t>
   </si>
   <si>
     <t>Valor</t>
-  </si>
-  <si>
-    <t>3.2. Importación y verificación de topología en HEC-RAS</t>
   </si>
   <si>
     <t>Visualizar independientemente los perfiles del cauce principal, cauce lateral 1 y cauce lateral 2. Identificar zonas que requieran ajustes como diques en posiciones incorrectas, diques faltantes, bancas erradas.</t>
@@ -86,19 +80,10 @@
     <t>Luego de depurado el modelo, comprimir como HECRAS_v1.zip</t>
   </si>
   <si>
-    <t>https://pruebacorreoescuelaingeduco.sharepoint.com/sites/HCMC/SitePages/HCMC0022.aspx</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Calificar sobre</t>
   </si>
   <si>
     <t>Calificación final</t>
-  </si>
-  <si>
-    <t>Crear un único reporte en Adobe Acrobat que muestre capturas de pantalla detalladas del proceso constructivo del modelo hidráulico, la depuración realizada y las secciones transversales de todo el modelo; nombrar como HCMC0022.pdf. Incluir portada, tabla de contenido, numeración de páginas y observaciones detalladas.</t>
   </si>
   <si>
     <t>Calificación Instructor</t>
@@ -122,49 +107,40 @@
     <t>Grupo 5</t>
   </si>
   <si>
-    <t>Crear un modelo en HEC-RAS e importar la geometría desde el archivo de datos GIS2RAS.RASImport.sdf obtenido de HEC-GeoRAS. Nombrar el modelo como HECRAS_v1. (no requerido si en entrega anterior realizó la creación del modelo en RAS Mapper)</t>
+    <t>Calificación: 3.2. Verificación de topología en HEC-RAS</t>
   </si>
   <si>
-    <t>Para la correcta modelación hidráulica, recomiendo colocar diques en las zonas naturales en donde se pueda observar la sección principal.</t>
+    <t>M03A02</t>
   </si>
   <si>
-    <t>Para la correcta modelación hidráulica, recomiendo colocar diques en las zonas naturales en donde se pueda observar la sección principal. En la sección de entrega falta colocar los diques.</t>
+    <t>Grupo 6</t>
   </si>
   <si>
-    <t>Faltan secciones por ajuste o inclusión de diques: secciones naturales de inicio y entrega, cauces naturales.</t>
+    <t>Grupo 7</t>
   </si>
   <si>
-    <t>Verificado con modelo RAS</t>
+    <t>Grupo 8</t>
   </si>
   <si>
-    <t>Informe sin verificación de perfiles en cauces laterales con localización de bancas y diques.</t>
+    <t>Grupo 9</t>
   </si>
   <si>
-    <t>Informe incompleto, sin verificación de perfiles en cauces laterales con chequeo de bancas y diques secciones naturales.</t>
+    <t>Grupo 10</t>
   </si>
   <si>
-    <t>Para la correcta modelación hidráulica, recomiendo colocar diques en las zonas naturales en donde se pueda observar la sección principal. Abscisado incorrecto en cauce principal, no se puede observar el perfil completo del cauce principal. Verificar geometría y observaciones indicadas en entrega anterior.</t>
+    <t>Grupo 11</t>
   </si>
   <si>
-    <t>Errores en en los cortes realizados en CIVIL 3D, la sección de entrega no es correcta y múltiples secciones con errores de empalme entre valle y cauce dominante.</t>
+    <t>Grupo 12</t>
   </si>
   <si>
-    <t>Múltiples puntos coalineados, secciones no depuradas.</t>
+    <t>Grupo 13</t>
   </si>
   <si>
-    <t>Posiciones incorrectas en la base del cauce dominante.</t>
+    <t>Grupo 14</t>
   </si>
   <si>
-    <t>Sin posición de diques.</t>
-  </si>
-  <si>
-    <t>Tramo natural sección de entrega separado de la sección diseñada. Integrar.</t>
-  </si>
-  <si>
-    <t>pdf vacío</t>
-  </si>
-  <si>
-    <t>Perfiles incompletos. Informe sin verificación de perfiles en cauces laterales con localización de bancas y diques. Sin limpieza de nodos completada. Sin diques.</t>
+    <t>Informe técnico mostrando las actividades desarrolladas en el orden presentado en esta actividad, junto con los análisis y recomendaciones realizadas, convierta a Adobe Acrobat (.pdf) y guarde en la carpeta /report del repositorio de datos del proyecto.</t>
   </si>
 </sst>
 </file>
@@ -172,10 +148,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,22 +222,28 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
-      <color theme="10"/>
+      <color theme="1"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -278,7 +260,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -392,15 +374,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </left>
@@ -457,6 +430,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -464,18 +461,46 @@
       <top style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
+      <left style="thin">
         <color indexed="64"/>
-      </bottom>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -485,7 +510,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -517,31 +542,14 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -550,7 +558,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -562,73 +570,91 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -673,7 +699,7 @@
           <c:strCache>
             <c:ptCount val="1"/>
             <c:pt idx="0">
-              <c:v>3.2. Importación y verificación de topología en HEC-RAS</c:v>
+              <c:v>Calificación: 3.2. Verificación de topología en HEC-RAS</c:v>
             </c:pt>
           </c:strCache>
         </c:strRef>
@@ -720,9 +746,9 @@
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="0.13451837270341208"/>
-          <c:y val="0.1223677777777778"/>
+          <c:y val="0.18508395061728394"/>
           <c:w val="0.83492607174103239"/>
-          <c:h val="0.61433916666666666"/>
+          <c:h val="0.55162314814814817"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -839,19 +865,19 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>4.7361111111111107</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.9444444444444446</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.9722222222222223</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.9444444444444446</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.6666666666666665</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1106,6 +1132,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1113,7 +1140,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1698,15 +1724,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>63636</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>901</xdr:rowOff>
+      <xdr:colOff>294434</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>81497</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>124299</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>27383</xdr:rowOff>
+      <xdr:colOff>361415</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>20718</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2034,7 +2060,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF50BAE-D7A1-4B9B-8511-69070389923C}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="B2:F22"/>
+  <dimension ref="B1:F21"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -2045,333 +2071,323 @@
     <col min="8" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="F1" s="31" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="2" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="B2" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="2:6" ht="46.15" x14ac:dyDescent="0.6">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="C5" s="35">
+        <v>5</v>
+      </c>
+      <c r="D5" s="19">
+        <f>Detalle!C14*C5/5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="21">
+        <f>AVERAGE(D5:E5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B6" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="35">
+        <v>5</v>
+      </c>
+      <c r="D6" s="19">
+        <f>Detalle!F14*C6/5</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="21">
+        <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B7" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="35">
+        <v>5</v>
+      </c>
+      <c r="D7" s="19">
+        <f>Detalle!I14*C7/5</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B8" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="C8" s="35">
+        <v>5</v>
+      </c>
+      <c r="D8" s="19">
+        <f>Detalle!L14*C8/5</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="35"/>
+      <c r="F8" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B5" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="30">
+      <c r="C9" s="35">
         <v>5</v>
       </c>
-      <c r="D5" s="24">
-        <f>Detalle!C15*C5/5</f>
-        <v>4.9722222222222223</v>
-      </c>
-      <c r="E5" s="30">
-        <v>4.5</v>
-      </c>
-      <c r="F5" s="31">
-        <f>AVERAGE(D5:E5)</f>
-        <v>4.7361111111111107</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B6" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="30">
+      <c r="D9" s="19">
+        <f>Detalle!O14*C9/5</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="35">
         <v>5</v>
       </c>
-      <c r="D6" s="24">
-        <f>Detalle!F15*C6/5</f>
-        <v>4.9444444444444446</v>
-      </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31">
-        <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
-        <v>4.9444444444444446</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B7" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="30">
+      <c r="D10" s="19">
+        <f>Detalle!R14*C10/5</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="35"/>
+      <c r="F10" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B11" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="35">
         <v>5</v>
       </c>
-      <c r="D7" s="24">
-        <f>Detalle!I15*C7/5</f>
-        <v>4.9722222222222223</v>
-      </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="31">
+      <c r="D11" s="19">
+        <f>Detalle!U14*C11/5</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="21">
         <f t="shared" si="0"/>
-        <v>4.9722222222222223</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B8" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B12" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="35">
         <v>5</v>
       </c>
-      <c r="D8" s="24">
-        <f>Detalle!L15*C8/5</f>
-        <v>4.9444444444444446</v>
-      </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="31">
+      <c r="D12" s="19">
+        <f>Detalle!X14*C12/5</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="21">
         <f t="shared" si="0"/>
-        <v>4.9444444444444446</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B9" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="35">
         <v>5</v>
       </c>
-      <c r="D9" s="24">
-        <f>Detalle!O15*C9/5</f>
-        <v>2.6666666666666665</v>
-      </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="31">
+      <c r="D13" s="19">
+        <f>Detalle!AA14*C13/5</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="35"/>
+      <c r="F13" s="21">
         <f t="shared" si="0"/>
-        <v>2.6666666666666665</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B10" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B14" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="35">
         <v>5</v>
       </c>
-      <c r="D10" s="24">
-        <f>Detalle!R15*C10/5</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="31">
+      <c r="D14" s="19">
+        <f>Detalle!AD14*C14/5</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="35"/>
+      <c r="F14" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B11" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="30">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B15" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="35">
         <v>5</v>
       </c>
-      <c r="D11" s="24">
-        <f>Detalle!U15*C11/5</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="31">
+      <c r="D15" s="19">
+        <f>Detalle!AG14*C15/5</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B12" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="30">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="35">
         <v>5</v>
       </c>
-      <c r="D12" s="24">
-        <f>Detalle!X15*C12/5</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="31">
+      <c r="D16" s="19">
+        <f>Detalle!AJ14*C16/5</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="35"/>
+      <c r="F16" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B13" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="30">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B17" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="35">
         <v>5</v>
       </c>
-      <c r="D13" s="24">
-        <f>Detalle!AA15*C13/5</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="31">
+      <c r="D17" s="19">
+        <f>Detalle!AM14*C17/5</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="35"/>
+      <c r="F17" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B14" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="30">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B18" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="36">
         <v>5</v>
       </c>
-      <c r="D14" s="24">
-        <f>Detalle!AD15*C14/5</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31">
+      <c r="D18" s="33">
+        <f>Detalle!AP14*C18/5</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="36"/>
+      <c r="F18" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B15" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="30">
-        <v>5</v>
-      </c>
-      <c r="D15" s="24">
-        <f>Detalle!AG15*C15/5</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B16" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="30">
-        <v>5</v>
-      </c>
-      <c r="D16" s="24">
-        <f>Detalle!AJ15*C16/5</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B17" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="30">
-        <v>5</v>
-      </c>
-      <c r="D17" s="24">
-        <f>Detalle!AM15*C17/5</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B18" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="30">
-        <v>5</v>
-      </c>
-      <c r="D18" s="24">
-        <f>Detalle!AP15*C18/5</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B19" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27">
-        <f>AVERAGE(D5:D18)</f>
-        <v>1.6071428571428574</v>
-      </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="28"/>
-    </row>
-    <row r="20" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B20" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
+    <row r="19" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B19" s="30" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F2,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F2," en GitHub."))</f>
+        <v>Ir a actividad  en GitHub.</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
-    <mergeCell ref="B20:F21"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B20" r:id="rId1" xr:uid="{895378D3-B9DA-4F07-AD83-A342D0AF1434}"/>
-  </hyperlinks>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17987CE-896A-4E26-83D1-1610B3259376}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AR50"/>
+  <dimension ref="A1:AR49"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="7" customWidth="1"/>
@@ -2410,8 +2426,9 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
-        <v>6</v>
+      <c r="B1" s="5" t="str">
+        <f>Calificacion!B2</f>
+        <v>Calificación: 3.2. Verificación de topología en HEC-RAS</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
@@ -2444,1119 +2461,853 @@
     </row>
     <row r="2" spans="1:44" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
-      <c r="B2" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="42" t="str">
+      <c r="B2" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="27" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="42" t="str">
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="27" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="42" t="str">
+      <c r="G2" s="28"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="27" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="43"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="42" t="str">
+      <c r="J2" s="28"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="27" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="43"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="42" t="str">
+      <c r="M2" s="28"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="27" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="42" t="str">
+      <c r="P2" s="28"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="27" t="str">
         <f>Calificacion!$B10</f>
-        <v>N/A</v>
-      </c>
-      <c r="S2" s="43"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="42" t="str">
+        <v>Grupo 6</v>
+      </c>
+      <c r="S2" s="28"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="27" t="str">
         <f>Calificacion!$B11</f>
-        <v>N/A</v>
-      </c>
-      <c r="V2" s="43"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="42" t="str">
+        <v>Grupo 7</v>
+      </c>
+      <c r="V2" s="28"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="27" t="str">
         <f>Calificacion!$B12</f>
-        <v>N/A</v>
-      </c>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="42" t="str">
+        <v>Grupo 8</v>
+      </c>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="27" t="str">
         <f>Calificacion!$B13</f>
-        <v>N/A</v>
-      </c>
-      <c r="AB2" s="43"/>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="42" t="str">
+        <v>Grupo 9</v>
+      </c>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="27" t="str">
         <f>Calificacion!$B14</f>
-        <v>N/A</v>
-      </c>
-      <c r="AE2" s="43"/>
-      <c r="AF2" s="44"/>
-      <c r="AG2" s="42" t="str">
+        <v>Grupo 10</v>
+      </c>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="27" t="str">
         <f>Calificacion!$B15</f>
-        <v>N/A</v>
-      </c>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="42" t="str">
+        <v>Grupo 11</v>
+      </c>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="27" t="str">
         <f>Calificacion!$B16</f>
-        <v>N/A</v>
-      </c>
-      <c r="AK2" s="43"/>
-      <c r="AL2" s="44"/>
-      <c r="AM2" s="42" t="str">
+        <v>Grupo 12</v>
+      </c>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="27" t="str">
         <f>Calificacion!$B17</f>
-        <v>N/A</v>
-      </c>
-      <c r="AN2" s="43"/>
-      <c r="AO2" s="44"/>
-      <c r="AP2" s="42" t="str">
+        <v>Grupo 13</v>
+      </c>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="29"/>
+      <c r="AP2" s="27" t="str">
         <f>Calificacion!$B18</f>
-        <v>N/A</v>
-      </c>
-      <c r="AQ2" s="43"/>
-      <c r="AR2" s="44"/>
+        <v>Grupo 14</v>
+      </c>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="29"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="46"/>
-      <c r="C3" s="15" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR3" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="B4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="15" t="s">
+      <c r="C4" s="37">
+        <v>0</v>
+      </c>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="37">
+        <v>0</v>
+      </c>
+      <c r="G4" s="38"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="37">
+        <v>0</v>
+      </c>
+      <c r="J4" s="38"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="37">
+        <v>0</v>
+      </c>
+      <c r="M4" s="38"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="37">
+        <v>0</v>
+      </c>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="37">
+        <v>0</v>
+      </c>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="37">
+        <v>0</v>
+      </c>
+      <c r="V4" s="38"/>
+      <c r="W4" s="39"/>
+      <c r="X4" s="37">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="39"/>
+      <c r="AA4" s="37">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="38"/>
+      <c r="AC4" s="39"/>
+      <c r="AD4" s="37">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="39"/>
+      <c r="AG4" s="37">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="39"/>
+      <c r="AJ4" s="37">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="38"/>
+      <c r="AL4" s="39"/>
+      <c r="AM4" s="37">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="38"/>
+      <c r="AO4" s="39"/>
+      <c r="AP4" s="37">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="38"/>
+      <c r="AR4" s="39"/>
+    </row>
+    <row r="5" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B5" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="37"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="37"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="37"/>
+      <c r="Y5" s="38"/>
+      <c r="Z5" s="39"/>
+      <c r="AA5" s="37"/>
+      <c r="AB5" s="38"/>
+      <c r="AC5" s="39"/>
+      <c r="AD5" s="37"/>
+      <c r="AE5" s="38"/>
+      <c r="AF5" s="39"/>
+      <c r="AG5" s="37"/>
+      <c r="AH5" s="38"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="37"/>
+      <c r="AK5" s="38"/>
+      <c r="AL5" s="39"/>
+      <c r="AM5" s="37"/>
+      <c r="AN5" s="38"/>
+      <c r="AO5" s="39"/>
+      <c r="AP5" s="37"/>
+      <c r="AQ5" s="38"/>
+      <c r="AR5" s="39"/>
+    </row>
+    <row r="6" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="37"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="37"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="37"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="39"/>
+      <c r="X6" s="37"/>
+      <c r="Y6" s="38"/>
+      <c r="Z6" s="39"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="38"/>
+      <c r="AC6" s="39"/>
+      <c r="AD6" s="37"/>
+      <c r="AE6" s="38"/>
+      <c r="AF6" s="39"/>
+      <c r="AG6" s="37"/>
+      <c r="AH6" s="38"/>
+      <c r="AI6" s="39"/>
+      <c r="AJ6" s="37"/>
+      <c r="AK6" s="38"/>
+      <c r="AL6" s="39"/>
+      <c r="AM6" s="37"/>
+      <c r="AN6" s="38"/>
+      <c r="AO6" s="39"/>
+      <c r="AP6" s="37"/>
+      <c r="AQ6" s="38"/>
+      <c r="AR6" s="39"/>
+    </row>
+    <row r="7" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="37"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="39"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="39"/>
+      <c r="X7" s="37"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="39"/>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="38"/>
+      <c r="AC7" s="39"/>
+      <c r="AD7" s="37"/>
+      <c r="AE7" s="38"/>
+      <c r="AF7" s="39"/>
+      <c r="AG7" s="37"/>
+      <c r="AH7" s="38"/>
+      <c r="AI7" s="39"/>
+      <c r="AJ7" s="37"/>
+      <c r="AK7" s="38"/>
+      <c r="AL7" s="39"/>
+      <c r="AM7" s="37"/>
+      <c r="AN7" s="38"/>
+      <c r="AO7" s="39"/>
+      <c r="AP7" s="37"/>
+      <c r="AQ7" s="38"/>
+      <c r="AR7" s="39"/>
+    </row>
+    <row r="8" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
+      <c r="B8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="37"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="37"/>
+      <c r="Y8" s="38"/>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="39"/>
+      <c r="AD8" s="37"/>
+      <c r="AE8" s="38"/>
+      <c r="AF8" s="39"/>
+      <c r="AG8" s="37"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="37"/>
+      <c r="AK8" s="38"/>
+      <c r="AL8" s="39"/>
+      <c r="AM8" s="37"/>
+      <c r="AN8" s="38"/>
+      <c r="AO8" s="39"/>
+      <c r="AP8" s="37"/>
+      <c r="AQ8" s="38"/>
+      <c r="AR8" s="39"/>
+    </row>
+    <row r="9" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="39"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="39"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="38"/>
+      <c r="Z9" s="39"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="38"/>
+      <c r="AC9" s="39"/>
+      <c r="AD9" s="37"/>
+      <c r="AE9" s="38"/>
+      <c r="AF9" s="39"/>
+      <c r="AG9" s="37"/>
+      <c r="AH9" s="38"/>
+      <c r="AI9" s="39"/>
+      <c r="AJ9" s="37"/>
+      <c r="AK9" s="38"/>
+      <c r="AL9" s="39"/>
+      <c r="AM9" s="37"/>
+      <c r="AN9" s="38"/>
+      <c r="AO9" s="39"/>
+      <c r="AP9" s="37"/>
+      <c r="AQ9" s="38"/>
+      <c r="AR9" s="39"/>
+    </row>
+    <row r="10" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="B10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="37"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="39"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="37"/>
+      <c r="AB10" s="38"/>
+      <c r="AC10" s="39"/>
+      <c r="AD10" s="37"/>
+      <c r="AE10" s="38"/>
+      <c r="AF10" s="39"/>
+      <c r="AG10" s="37"/>
+      <c r="AH10" s="38"/>
+      <c r="AI10" s="39"/>
+      <c r="AJ10" s="37"/>
+      <c r="AK10" s="38"/>
+      <c r="AL10" s="39"/>
+      <c r="AM10" s="37"/>
+      <c r="AN10" s="38"/>
+      <c r="AO10" s="39"/>
+      <c r="AP10" s="37"/>
+      <c r="AQ10" s="38"/>
+      <c r="AR10" s="39"/>
+    </row>
+    <row r="11" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B11" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="37"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="39"/>
+      <c r="U11" s="37"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="39"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="39"/>
+      <c r="AA11" s="37"/>
+      <c r="AB11" s="38"/>
+      <c r="AC11" s="39"/>
+      <c r="AD11" s="37"/>
+      <c r="AE11" s="38"/>
+      <c r="AF11" s="39"/>
+      <c r="AG11" s="37"/>
+      <c r="AH11" s="38"/>
+      <c r="AI11" s="39"/>
+      <c r="AJ11" s="37"/>
+      <c r="AK11" s="38"/>
+      <c r="AL11" s="39"/>
+      <c r="AM11" s="37"/>
+      <c r="AN11" s="38"/>
+      <c r="AO11" s="39"/>
+      <c r="AP11" s="37"/>
+      <c r="AQ11" s="38"/>
+      <c r="AR11" s="39"/>
+    </row>
+    <row r="12" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="B12" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="37"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="37"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="39"/>
+      <c r="U12" s="37"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="37"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="39"/>
+      <c r="AA12" s="37"/>
+      <c r="AB12" s="38"/>
+      <c r="AC12" s="39"/>
+      <c r="AD12" s="37"/>
+      <c r="AE12" s="38"/>
+      <c r="AF12" s="39"/>
+      <c r="AG12" s="37"/>
+      <c r="AH12" s="38"/>
+      <c r="AI12" s="39"/>
+      <c r="AJ12" s="37"/>
+      <c r="AK12" s="38"/>
+      <c r="AL12" s="39"/>
+      <c r="AM12" s="37"/>
+      <c r="AN12" s="38"/>
+      <c r="AO12" s="39"/>
+      <c r="AP12" s="37"/>
+      <c r="AQ12" s="38"/>
+      <c r="AR12" s="39"/>
+    </row>
+    <row r="13" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B13" s="40"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="41"/>
+      <c r="V13" s="42"/>
+      <c r="W13" s="43"/>
+      <c r="X13" s="41"/>
+      <c r="Y13" s="42"/>
+      <c r="Z13" s="43"/>
+      <c r="AA13" s="41"/>
+      <c r="AB13" s="42"/>
+      <c r="AC13" s="43"/>
+      <c r="AD13" s="41"/>
+      <c r="AE13" s="42"/>
+      <c r="AF13" s="43"/>
+      <c r="AG13" s="41"/>
+      <c r="AH13" s="42"/>
+      <c r="AI13" s="43"/>
+      <c r="AJ13" s="41"/>
+      <c r="AK13" s="42"/>
+      <c r="AL13" s="43"/>
+      <c r="AM13" s="41"/>
+      <c r="AN13" s="42"/>
+      <c r="AO13" s="43"/>
+      <c r="AP13" s="41"/>
+      <c r="AQ13" s="42"/>
+      <c r="AR13" s="43"/>
+    </row>
+    <row r="14" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="2"/>
+      <c r="B14" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="V3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="X3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR3" s="16" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="17"/>
-      <c r="AB4" s="11"/>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="17"/>
-      <c r="AE4" s="11"/>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="17"/>
-      <c r="AH4" s="11"/>
-      <c r="AI4" s="12"/>
-      <c r="AJ4" s="17"/>
-      <c r="AK4" s="11"/>
-      <c r="AL4" s="12"/>
-      <c r="AM4" s="17"/>
-      <c r="AN4" s="11"/>
-      <c r="AO4" s="12"/>
-      <c r="AP4" s="17"/>
-      <c r="AQ4" s="11"/>
-      <c r="AR4" s="12"/>
-    </row>
-    <row r="5" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
-      <c r="B5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="17">
-        <v>5</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="17">
-        <v>5</v>
-      </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="17">
-        <v>5</v>
-      </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="17">
-        <v>5</v>
-      </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="33">
-        <v>3.5</v>
-      </c>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="R5" s="17">
-        <v>0</v>
-      </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="18"/>
-      <c r="U5" s="17">
-        <v>0</v>
-      </c>
-      <c r="V5" s="11"/>
-      <c r="W5" s="18"/>
-      <c r="X5" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="11"/>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="18"/>
-      <c r="AD5" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="18"/>
-      <c r="AG5" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="18"/>
-      <c r="AJ5" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="11"/>
-      <c r="AL5" s="18"/>
-      <c r="AM5" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="11"/>
-      <c r="AO5" s="18"/>
-      <c r="AP5" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="11"/>
-      <c r="AR5" s="18"/>
-    </row>
-    <row r="6" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
-      <c r="B6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="17">
-        <v>5</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="17">
-        <v>5</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="17">
-        <v>5</v>
-      </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="17">
-        <v>5</v>
-      </c>
-      <c r="M6" s="11"/>
-      <c r="N6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6" s="33">
-        <v>3</v>
-      </c>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R6" s="17">
-        <v>0</v>
-      </c>
-      <c r="S6" s="11"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="17">
-        <v>0</v>
-      </c>
-      <c r="V6" s="11"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="11"/>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="12"/>
-      <c r="AJ6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="11"/>
-      <c r="AL6" s="12"/>
-      <c r="AM6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="11"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="11"/>
-      <c r="AR6" s="12"/>
-    </row>
-    <row r="7" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="17">
-        <v>5</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="17">
-        <v>5</v>
-      </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="17">
-        <v>5</v>
-      </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="17">
-        <v>5</v>
-      </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="33">
-        <v>2</v>
-      </c>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="R7" s="17">
-        <v>0</v>
-      </c>
-      <c r="S7" s="11"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="17">
-        <v>0</v>
-      </c>
-      <c r="V7" s="11"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="11"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="12"/>
-      <c r="AJ7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="11"/>
-      <c r="AL7" s="12"/>
-      <c r="AM7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="11"/>
-      <c r="AO7" s="12"/>
-      <c r="AP7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="11"/>
-      <c r="AR7" s="12"/>
-    </row>
-    <row r="8" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B8" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="17">
-        <v>5</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="17">
-        <v>5</v>
-      </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="17">
-        <v>5</v>
-      </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="17">
-        <v>5</v>
-      </c>
-      <c r="M8" s="11"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="33">
-        <v>2</v>
-      </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="R8" s="17">
-        <v>0</v>
-      </c>
-      <c r="S8" s="11"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="17">
-        <v>0</v>
-      </c>
-      <c r="V8" s="11"/>
-      <c r="W8" s="18"/>
-      <c r="X8" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="11"/>
-      <c r="Z8" s="18"/>
-      <c r="AA8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="18"/>
-      <c r="AD8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="18"/>
-      <c r="AG8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="18"/>
-      <c r="AJ8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="11"/>
-      <c r="AL8" s="18"/>
-      <c r="AM8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="11"/>
-      <c r="AO8" s="18"/>
-      <c r="AP8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="11"/>
-      <c r="AR8" s="18"/>
-    </row>
-    <row r="9" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
-      <c r="B9" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="33">
-        <v>4.75</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="33">
-        <v>4.75</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="33">
-        <v>4.75</v>
-      </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="33">
-        <v>4.75</v>
-      </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="O9" s="33">
-        <v>0</v>
-      </c>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="R9" s="17">
-        <v>0</v>
-      </c>
-      <c r="S9" s="11"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="17">
-        <v>0</v>
-      </c>
-      <c r="V9" s="11"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="11"/>
-      <c r="Z9" s="18"/>
-      <c r="AA9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="18"/>
-      <c r="AD9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="18"/>
-      <c r="AG9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="11"/>
-      <c r="AI9" s="18"/>
-      <c r="AJ9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="11"/>
-      <c r="AL9" s="18"/>
-      <c r="AM9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="11"/>
-      <c r="AO9" s="18"/>
-      <c r="AP9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="11"/>
-      <c r="AR9" s="18"/>
-    </row>
-    <row r="10" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B10" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="17">
-        <v>5</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="17">
-        <v>5</v>
-      </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="17">
-        <v>5</v>
-      </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="17">
-        <v>5</v>
-      </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="33">
-        <v>4.5</v>
-      </c>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="R10" s="17">
-        <v>0</v>
-      </c>
-      <c r="S10" s="11"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="17">
-        <v>0</v>
-      </c>
-      <c r="V10" s="11"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="11"/>
-      <c r="Z10" s="18"/>
-      <c r="AA10" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="18"/>
-      <c r="AD10" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="18"/>
-      <c r="AG10" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="11"/>
-      <c r="AI10" s="18"/>
-      <c r="AJ10" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="11"/>
-      <c r="AL10" s="18"/>
-      <c r="AM10" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="11"/>
-      <c r="AO10" s="18"/>
-      <c r="AP10" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="11"/>
-      <c r="AR10" s="18"/>
-    </row>
-    <row r="11" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="B11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="17">
-        <v>5</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="17">
-        <v>5</v>
-      </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="17">
-        <v>5</v>
-      </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="17">
-        <v>5</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="33">
-        <v>0</v>
-      </c>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="R11" s="17">
-        <v>0</v>
-      </c>
-      <c r="S11" s="11"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="17">
-        <v>0</v>
-      </c>
-      <c r="V11" s="11"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="11"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="12"/>
-      <c r="AD11" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="11"/>
-      <c r="AI11" s="12"/>
-      <c r="AJ11" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="11"/>
-      <c r="AL11" s="12"/>
-      <c r="AM11" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="11"/>
-      <c r="AO11" s="12"/>
-      <c r="AP11" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="11"/>
-      <c r="AR11" s="12"/>
-    </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B12" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="17">
-        <v>5</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="17">
-        <v>5</v>
-      </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="17">
-        <v>5</v>
-      </c>
-      <c r="J12" s="11"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="17">
-        <v>5</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="17">
-        <v>5</v>
-      </c>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="17">
-        <v>0</v>
-      </c>
-      <c r="S12" s="11"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="17">
-        <v>0</v>
-      </c>
-      <c r="V12" s="11"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="12"/>
-      <c r="AD12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="12"/>
-      <c r="AG12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="11"/>
-      <c r="AI12" s="12"/>
-      <c r="AJ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="11"/>
-      <c r="AL12" s="12"/>
-      <c r="AM12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="11"/>
-      <c r="AO12" s="12"/>
-      <c r="AP12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="11"/>
-      <c r="AR12" s="12"/>
-    </row>
-    <row r="13" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
-      <c r="B13" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="17">
-        <v>5</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="33">
-        <v>4.75</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="17">
-        <v>5</v>
-      </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="33">
-        <v>4.75</v>
-      </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O13" s="33">
-        <v>4</v>
-      </c>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="R13" s="17">
-        <v>0</v>
-      </c>
-      <c r="S13" s="11"/>
-      <c r="T13" s="18"/>
-      <c r="U13" s="17">
-        <v>0</v>
-      </c>
-      <c r="V13" s="11"/>
-      <c r="W13" s="18"/>
-      <c r="X13" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="11"/>
-      <c r="Z13" s="18"/>
-      <c r="AA13" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="18"/>
-      <c r="AD13" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="18"/>
-      <c r="AG13" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="11"/>
-      <c r="AI13" s="18"/>
-      <c r="AJ13" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="11"/>
-      <c r="AL13" s="18"/>
-      <c r="AM13" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="11"/>
-      <c r="AO13" s="18"/>
-      <c r="AP13" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="11"/>
-      <c r="AR13" s="18"/>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B14" s="13"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="17"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="17"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="17"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="12"/>
-      <c r="AG14" s="17"/>
-      <c r="AH14" s="11"/>
-      <c r="AI14" s="12"/>
-      <c r="AJ14" s="17"/>
-      <c r="AK14" s="11"/>
-      <c r="AL14" s="12"/>
-      <c r="AM14" s="17"/>
-      <c r="AN14" s="11"/>
-      <c r="AO14" s="12"/>
-      <c r="AP14" s="17"/>
-      <c r="AQ14" s="11"/>
-      <c r="AR14" s="12"/>
-    </row>
-    <row r="15" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="2"/>
-      <c r="B15" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="39">
-        <f>AVERAGE(C4:C14)</f>
-        <v>4.9722222222222223</v>
-      </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="39">
-        <f>AVERAGE(F4:F14)</f>
-        <v>4.9444444444444446</v>
-      </c>
-      <c r="G15" s="40"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="39">
-        <f>AVERAGE(I4:I14)</f>
-        <v>4.9722222222222223</v>
-      </c>
-      <c r="J15" s="40"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="39">
-        <f>AVERAGE(L4:L14)</f>
-        <v>4.9444444444444446</v>
-      </c>
-      <c r="M15" s="40"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="39">
-        <f>AVERAGE(O4:O14)</f>
-        <v>2.6666666666666665</v>
-      </c>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="39">
-        <f>AVERAGE(R4:R14)</f>
-        <v>0</v>
-      </c>
-      <c r="S15" s="40"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="39">
-        <f>AVERAGE(U4:U14)</f>
-        <v>0</v>
-      </c>
-      <c r="V15" s="40"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="39">
-        <f>AVERAGE(X4:X14)</f>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="40"/>
-      <c r="Z15" s="41"/>
-      <c r="AA15" s="39">
-        <f>AVERAGE(AA4:AA14)</f>
-        <v>0</v>
-      </c>
-      <c r="AB15" s="40"/>
-      <c r="AC15" s="41"/>
-      <c r="AD15" s="39">
-        <f>AVERAGE(AD4:AD14)</f>
-        <v>0</v>
-      </c>
-      <c r="AE15" s="40"/>
-      <c r="AF15" s="41"/>
-      <c r="AG15" s="39">
-        <f>AVERAGE(AG4:AG14)</f>
-        <v>0</v>
-      </c>
-      <c r="AH15" s="40"/>
-      <c r="AI15" s="41"/>
-      <c r="AJ15" s="39">
-        <f>AVERAGE(AJ4:AJ14)</f>
-        <v>0</v>
-      </c>
-      <c r="AK15" s="40"/>
-      <c r="AL15" s="41"/>
-      <c r="AM15" s="39">
-        <f>AVERAGE(AM4:AM14)</f>
-        <v>0</v>
-      </c>
-      <c r="AN15" s="40"/>
-      <c r="AO15" s="41"/>
-      <c r="AP15" s="39">
-        <f>AVERAGE(AP4:AP14)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="40"/>
-      <c r="AR15" s="41"/>
+      <c r="C14" s="45">
+        <f>AVERAGE(C4:C13)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="45">
+        <f>AVERAGE(F4:F13)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="45"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="45">
+        <f>AVERAGE(I4:I13)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="45"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="45">
+        <f>AVERAGE(L4:L13)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="45"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="45">
+        <f>AVERAGE(O4:O13)</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="45"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="45">
+        <f>AVERAGE(R4:R13)</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="45"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="45">
+        <f>AVERAGE(U4:U13)</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="45"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="45">
+        <f>AVERAGE(X4:X13)</f>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="45"/>
+      <c r="Z14" s="46"/>
+      <c r="AA14" s="45">
+        <f>AVERAGE(AA4:AA13)</f>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="45"/>
+      <c r="AC14" s="46"/>
+      <c r="AD14" s="45">
+        <f>AVERAGE(AD4:AD13)</f>
+        <v>0</v>
+      </c>
+      <c r="AE14" s="45"/>
+      <c r="AF14" s="46"/>
+      <c r="AG14" s="45">
+        <f>AVERAGE(AG4:AG13)</f>
+        <v>0</v>
+      </c>
+      <c r="AH14" s="45"/>
+      <c r="AI14" s="46"/>
+      <c r="AJ14" s="45">
+        <f>AVERAGE(AJ4:AJ13)</f>
+        <v>0</v>
+      </c>
+      <c r="AK14" s="45"/>
+      <c r="AL14" s="46"/>
+      <c r="AM14" s="45">
+        <f>AVERAGE(AM4:AM13)</f>
+        <v>0</v>
+      </c>
+      <c r="AN14" s="45"/>
+      <c r="AO14" s="46"/>
+      <c r="AP14" s="45">
+        <f>AVERAGE(AP4:AP13)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="45"/>
+      <c r="AR14" s="46"/>
+    </row>
+    <row r="15" spans="1:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="6"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="9"/>
+      <c r="AB15" s="9"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="9"/>
+      <c r="AE15" s="9"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="9"/>
+      <c r="AH15" s="9"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="9"/>
+      <c r="AK15" s="9"/>
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="9"/>
+      <c r="AN15" s="9"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="9"/>
+      <c r="AQ15" s="9"/>
+      <c r="AR15" s="3"/>
     </row>
     <row r="16" spans="1:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B16" s="6"/>
@@ -5088,59 +4839,27 @@
       <c r="AQ49" s="9"/>
       <c r="AR49" s="3"/>
     </row>
-    <row r="50" spans="2:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="6"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="9"/>
-      <c r="S50" s="9"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="3"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="3"/>
-      <c r="AD50" s="9"/>
-      <c r="AE50" s="9"/>
-      <c r="AF50" s="3"/>
-      <c r="AG50" s="9"/>
-      <c r="AH50" s="9"/>
-      <c r="AI50" s="3"/>
-      <c r="AJ50" s="9"/>
-      <c r="AK50" s="9"/>
-      <c r="AL50" s="3"/>
-      <c r="AM50" s="9"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="3"/>
-      <c r="AP50" s="9"/>
-      <c r="AQ50" s="9"/>
-      <c r="AR50" s="3"/>
-    </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="AM14:AO14"/>
+    <mergeCell ref="X14:Z14"/>
+    <mergeCell ref="AA14:AC14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AG14:AI14"/>
+    <mergeCell ref="AJ14:AL14"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:Q14"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AP15:AR15"/>
+    <mergeCell ref="AP14:AR14"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:H14"/>
     <mergeCell ref="AJ2:AL2"/>
     <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="AG2:AI2"/>
@@ -5151,19 +4870,6 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="AM15:AO15"/>
-    <mergeCell ref="X15:Z15"/>
-    <mergeCell ref="AA15:AC15"/>
-    <mergeCell ref="AD15:AF15"/>
-    <mergeCell ref="AG15:AI15"/>
-    <mergeCell ref="AJ15:AL15"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M03A02/M03A02_VerificacionTopologia.xlsx
+++ b/activity/M03A02/M03A02_VerificacionTopologia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD59455-5145-42D5-B58A-377D41D7A8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEABBF5-20A5-4A4D-BAD1-BC54D7D60486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="630" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -579,30 +579,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -650,11 +626,35 @@
     <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2072,25 +2072,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="23" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="4" spans="2:6" ht="46.15" x14ac:dyDescent="0.6">
       <c r="B4" s="15" t="s">
@@ -2113,14 +2113,14 @@
       <c r="B5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="27">
         <v>5</v>
       </c>
       <c r="D5" s="19">
         <f>Detalle!C14*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="27"/>
       <c r="F5" s="21">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2130,14 +2130,14 @@
       <c r="B6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="27">
         <v>5</v>
       </c>
       <c r="D6" s="19">
         <f>Detalle!F14*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="35"/>
+      <c r="E6" s="27"/>
       <c r="F6" s="21">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2147,14 +2147,14 @@
       <c r="B7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="27">
         <v>5</v>
       </c>
       <c r="D7" s="19">
         <f>Detalle!I14*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="35"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2164,14 +2164,14 @@
       <c r="B8" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="27">
         <v>5</v>
       </c>
       <c r="D8" s="19">
         <f>Detalle!L14*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="35"/>
+      <c r="E8" s="27"/>
       <c r="F8" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2181,14 +2181,14 @@
       <c r="B9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="27">
         <v>5</v>
       </c>
       <c r="D9" s="19">
         <f>Detalle!O14*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="35"/>
+      <c r="E9" s="27"/>
       <c r="F9" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2198,14 +2198,14 @@
       <c r="B10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="27">
         <v>5</v>
       </c>
       <c r="D10" s="19">
         <f>Detalle!R14*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="35"/>
+      <c r="E10" s="27"/>
       <c r="F10" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2215,14 +2215,14 @@
       <c r="B11" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="27">
         <v>5</v>
       </c>
       <c r="D11" s="19">
         <f>Detalle!U14*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="35"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2232,14 +2232,14 @@
       <c r="B12" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="27">
         <v>5</v>
       </c>
       <c r="D12" s="19">
         <f>Detalle!X14*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="35"/>
+      <c r="E12" s="27"/>
       <c r="F12" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2249,14 +2249,14 @@
       <c r="B13" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="27">
         <v>5</v>
       </c>
       <c r="D13" s="19">
         <f>Detalle!AA14*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="35"/>
+      <c r="E13" s="27"/>
       <c r="F13" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2266,14 +2266,14 @@
       <c r="B14" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="27">
         <v>5</v>
       </c>
       <c r="D14" s="19">
         <f>Detalle!AD14*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="35"/>
+      <c r="E14" s="27"/>
       <c r="F14" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2283,14 +2283,14 @@
       <c r="B15" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="27">
         <v>5</v>
       </c>
       <c r="D15" s="19">
         <f>Detalle!AG14*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="35"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2300,14 +2300,14 @@
       <c r="B16" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="27">
         <v>5</v>
       </c>
       <c r="D16" s="19">
         <f>Detalle!AJ14*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="35"/>
+      <c r="E16" s="27"/>
       <c r="F16" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2317,52 +2317,52 @@
       <c r="B17" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="27">
         <v>5</v>
       </c>
       <c r="D17" s="19">
         <f>Detalle!AM14*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="35"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="28">
         <v>5</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="25">
         <f>Detalle!AP14*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="34">
+      <c r="E18" s="28"/>
+      <c r="F18" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B19" s="30" t="str">
+      <c r="B19" s="39" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F2,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F2," en GitHub."))</f>
         <v>Ir a actividad  en GitHub.</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B21" s="20"/>
@@ -2461,96 +2461,96 @@
     </row>
     <row r="2" spans="1:44" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="27" t="str">
+      <c r="C2" s="42" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="27" t="str">
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="42" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="27" t="str">
+      <c r="G2" s="43"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="42" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="27" t="str">
+      <c r="J2" s="43"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="42" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="27" t="str">
+      <c r="M2" s="43"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="42" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="27" t="str">
+      <c r="P2" s="43"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="42" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="28"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="27" t="str">
+      <c r="S2" s="43"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="42" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="28"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="27" t="str">
+      <c r="V2" s="43"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="42" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="27" t="str">
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="42" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="27" t="str">
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="42" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="27" t="str">
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="42" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="27" t="str">
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="42" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="27" t="str">
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="42" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="27" t="str">
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="42" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="29"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="44"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="26"/>
+      <c r="B3" s="46"/>
       <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
@@ -2682,587 +2682,587 @@
       <c r="B4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="37">
-        <v>0</v>
-      </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="37">
-        <v>0</v>
-      </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="37">
-        <v>0</v>
-      </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="37">
-        <v>0</v>
-      </c>
-      <c r="M4" s="38"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="37">
-        <v>0</v>
-      </c>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="37">
-        <v>0</v>
-      </c>
-      <c r="S4" s="38"/>
-      <c r="T4" s="39"/>
-      <c r="U4" s="37">
-        <v>0</v>
-      </c>
-      <c r="V4" s="38"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="37">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="39"/>
-      <c r="AA4" s="37">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="39"/>
-      <c r="AD4" s="37">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="39"/>
-      <c r="AG4" s="37">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="39"/>
-      <c r="AJ4" s="37">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="39"/>
-      <c r="AM4" s="37">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="39"/>
-      <c r="AP4" s="37">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="39"/>
+      <c r="C4" s="29">
+        <v>0</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="29">
+        <v>0</v>
+      </c>
+      <c r="G4" s="30"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="29">
+        <v>0</v>
+      </c>
+      <c r="J4" s="30"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="29">
+        <v>0</v>
+      </c>
+      <c r="M4" s="30"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="29">
+        <v>0</v>
+      </c>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="29">
+        <v>0</v>
+      </c>
+      <c r="S4" s="30"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="29">
+        <v>0</v>
+      </c>
+      <c r="V4" s="30"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="31"/>
+      <c r="AG4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="31"/>
+      <c r="AJ4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="31"/>
+      <c r="AM4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="31"/>
+      <c r="AP4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="30"/>
+      <c r="AR4" s="31"/>
     </row>
     <row r="5" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="39"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="39"/>
-      <c r="X5" s="37"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="39"/>
-      <c r="AA5" s="37"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="39"/>
-      <c r="AD5" s="37"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="39"/>
-      <c r="AG5" s="37"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="39"/>
-      <c r="AJ5" s="37"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="39"/>
-      <c r="AM5" s="37"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="39"/>
-      <c r="AP5" s="37"/>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="39"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="31"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="31"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="30"/>
+      <c r="AR5" s="31"/>
     </row>
     <row r="6" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="39"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="39"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="39"/>
-      <c r="AA6" s="37"/>
-      <c r="AB6" s="38"/>
-      <c r="AC6" s="39"/>
-      <c r="AD6" s="37"/>
-      <c r="AE6" s="38"/>
-      <c r="AF6" s="39"/>
-      <c r="AG6" s="37"/>
-      <c r="AH6" s="38"/>
-      <c r="AI6" s="39"/>
-      <c r="AJ6" s="37"/>
-      <c r="AK6" s="38"/>
-      <c r="AL6" s="39"/>
-      <c r="AM6" s="37"/>
-      <c r="AN6" s="38"/>
-      <c r="AO6" s="39"/>
-      <c r="AP6" s="37"/>
-      <c r="AQ6" s="38"/>
-      <c r="AR6" s="39"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="31"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="31"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="31"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="30"/>
+      <c r="AO6" s="31"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="30"/>
+      <c r="AR6" s="31"/>
     </row>
     <row r="7" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="37"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="39"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="39"/>
-      <c r="AA7" s="37"/>
-      <c r="AB7" s="38"/>
-      <c r="AC7" s="39"/>
-      <c r="AD7" s="37"/>
-      <c r="AE7" s="38"/>
-      <c r="AF7" s="39"/>
-      <c r="AG7" s="37"/>
-      <c r="AH7" s="38"/>
-      <c r="AI7" s="39"/>
-      <c r="AJ7" s="37"/>
-      <c r="AK7" s="38"/>
-      <c r="AL7" s="39"/>
-      <c r="AM7" s="37"/>
-      <c r="AN7" s="38"/>
-      <c r="AO7" s="39"/>
-      <c r="AP7" s="37"/>
-      <c r="AQ7" s="38"/>
-      <c r="AR7" s="39"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="31"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="31"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="31"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="31"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="30"/>
+      <c r="AR7" s="31"/>
     </row>
     <row r="8" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="39"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="39"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="38"/>
-      <c r="Z8" s="39"/>
-      <c r="AA8" s="37"/>
-      <c r="AB8" s="38"/>
-      <c r="AC8" s="39"/>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="38"/>
-      <c r="AF8" s="39"/>
-      <c r="AG8" s="37"/>
-      <c r="AH8" s="38"/>
-      <c r="AI8" s="39"/>
-      <c r="AJ8" s="37"/>
-      <c r="AK8" s="38"/>
-      <c r="AL8" s="39"/>
-      <c r="AM8" s="37"/>
-      <c r="AN8" s="38"/>
-      <c r="AO8" s="39"/>
-      <c r="AP8" s="37"/>
-      <c r="AQ8" s="38"/>
-      <c r="AR8" s="39"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="29"/>
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="31"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="31"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="30"/>
+      <c r="AO8" s="31"/>
+      <c r="AP8" s="29"/>
+      <c r="AQ8" s="30"/>
+      <c r="AR8" s="31"/>
     </row>
     <row r="9" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="38"/>
-      <c r="T9" s="39"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="39"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="38"/>
-      <c r="Z9" s="39"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="38"/>
-      <c r="AC9" s="39"/>
-      <c r="AD9" s="37"/>
-      <c r="AE9" s="38"/>
-      <c r="AF9" s="39"/>
-      <c r="AG9" s="37"/>
-      <c r="AH9" s="38"/>
-      <c r="AI9" s="39"/>
-      <c r="AJ9" s="37"/>
-      <c r="AK9" s="38"/>
-      <c r="AL9" s="39"/>
-      <c r="AM9" s="37"/>
-      <c r="AN9" s="38"/>
-      <c r="AO9" s="39"/>
-      <c r="AP9" s="37"/>
-      <c r="AQ9" s="38"/>
-      <c r="AR9" s="39"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="31"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="31"/>
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="30"/>
+      <c r="AR9" s="31"/>
     </row>
     <row r="10" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="38"/>
-      <c r="T10" s="39"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="39"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="38"/>
-      <c r="Z10" s="39"/>
-      <c r="AA10" s="37"/>
-      <c r="AB10" s="38"/>
-      <c r="AC10" s="39"/>
-      <c r="AD10" s="37"/>
-      <c r="AE10" s="38"/>
-      <c r="AF10" s="39"/>
-      <c r="AG10" s="37"/>
-      <c r="AH10" s="38"/>
-      <c r="AI10" s="39"/>
-      <c r="AJ10" s="37"/>
-      <c r="AK10" s="38"/>
-      <c r="AL10" s="39"/>
-      <c r="AM10" s="37"/>
-      <c r="AN10" s="38"/>
-      <c r="AO10" s="39"/>
-      <c r="AP10" s="37"/>
-      <c r="AQ10" s="38"/>
-      <c r="AR10" s="39"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="31"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="30"/>
+      <c r="AO10" s="31"/>
+      <c r="AP10" s="29"/>
+      <c r="AQ10" s="30"/>
+      <c r="AR10" s="31"/>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="39"/>
-      <c r="U11" s="37"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="38"/>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="37"/>
-      <c r="AB11" s="38"/>
-      <c r="AC11" s="39"/>
-      <c r="AD11" s="37"/>
-      <c r="AE11" s="38"/>
-      <c r="AF11" s="39"/>
-      <c r="AG11" s="37"/>
-      <c r="AH11" s="38"/>
-      <c r="AI11" s="39"/>
-      <c r="AJ11" s="37"/>
-      <c r="AK11" s="38"/>
-      <c r="AL11" s="39"/>
-      <c r="AM11" s="37"/>
-      <c r="AN11" s="38"/>
-      <c r="AO11" s="39"/>
-      <c r="AP11" s="37"/>
-      <c r="AQ11" s="38"/>
-      <c r="AR11" s="39"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="29"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="30"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="29"/>
+      <c r="AQ11" s="30"/>
+      <c r="AR11" s="31"/>
     </row>
     <row r="12" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="37"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="37"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="37"/>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="37"/>
-      <c r="AH12" s="38"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="37"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="37"/>
-      <c r="AN12" s="38"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="37"/>
-      <c r="AQ12" s="38"/>
-      <c r="AR12" s="39"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="29"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="29"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="29"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="29"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="30"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="29"/>
+      <c r="AQ12" s="30"/>
+      <c r="AR12" s="31"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="41"/>
-      <c r="V13" s="42"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="41"/>
-      <c r="Y13" s="42"/>
-      <c r="Z13" s="43"/>
-      <c r="AA13" s="41"/>
-      <c r="AB13" s="42"/>
-      <c r="AC13" s="43"/>
-      <c r="AD13" s="41"/>
-      <c r="AE13" s="42"/>
-      <c r="AF13" s="43"/>
-      <c r="AG13" s="41"/>
-      <c r="AH13" s="42"/>
-      <c r="AI13" s="43"/>
-      <c r="AJ13" s="41"/>
-      <c r="AK13" s="42"/>
-      <c r="AL13" s="43"/>
-      <c r="AM13" s="41"/>
-      <c r="AN13" s="42"/>
-      <c r="AO13" s="43"/>
-      <c r="AP13" s="41"/>
-      <c r="AQ13" s="42"/>
-      <c r="AR13" s="43"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="33"/>
+      <c r="V13" s="34"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="33"/>
+      <c r="Y13" s="34"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="33"/>
+      <c r="AB13" s="34"/>
+      <c r="AC13" s="35"/>
+      <c r="AD13" s="33"/>
+      <c r="AE13" s="34"/>
+      <c r="AF13" s="35"/>
+      <c r="AG13" s="33"/>
+      <c r="AH13" s="34"/>
+      <c r="AI13" s="35"/>
+      <c r="AJ13" s="33"/>
+      <c r="AK13" s="34"/>
+      <c r="AL13" s="35"/>
+      <c r="AM13" s="33"/>
+      <c r="AN13" s="34"/>
+      <c r="AO13" s="35"/>
+      <c r="AP13" s="33"/>
+      <c r="AQ13" s="34"/>
+      <c r="AR13" s="35"/>
     </row>
     <row r="14" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2"/>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="40">
         <f>AVERAGE(C4:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="45">
+      <c r="D14" s="40"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="40">
         <f>AVERAGE(F4:F13)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="45">
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="40">
         <f>AVERAGE(I4:I13)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="45"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="45">
+      <c r="J14" s="40"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="40">
         <f>AVERAGE(L4:L13)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="45"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="45">
+      <c r="M14" s="40"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="40">
         <f>AVERAGE(O4:O13)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="45">
+      <c r="P14" s="40"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="40">
         <f>AVERAGE(R4:R13)</f>
         <v>0</v>
       </c>
-      <c r="S14" s="45"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="45">
+      <c r="S14" s="40"/>
+      <c r="T14" s="41"/>
+      <c r="U14" s="40">
         <f>AVERAGE(U4:U13)</f>
         <v>0</v>
       </c>
-      <c r="V14" s="45"/>
-      <c r="W14" s="46"/>
-      <c r="X14" s="45">
+      <c r="V14" s="40"/>
+      <c r="W14" s="41"/>
+      <c r="X14" s="40">
         <f>AVERAGE(X4:X13)</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="45"/>
-      <c r="Z14" s="46"/>
-      <c r="AA14" s="45">
+      <c r="Y14" s="40"/>
+      <c r="Z14" s="41"/>
+      <c r="AA14" s="40">
         <f>AVERAGE(AA4:AA13)</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="45"/>
-      <c r="AC14" s="46"/>
-      <c r="AD14" s="45">
+      <c r="AB14" s="40"/>
+      <c r="AC14" s="41"/>
+      <c r="AD14" s="40">
         <f>AVERAGE(AD4:AD13)</f>
         <v>0</v>
       </c>
-      <c r="AE14" s="45"/>
-      <c r="AF14" s="46"/>
-      <c r="AG14" s="45">
+      <c r="AE14" s="40"/>
+      <c r="AF14" s="41"/>
+      <c r="AG14" s="40">
         <f>AVERAGE(AG4:AG13)</f>
         <v>0</v>
       </c>
-      <c r="AH14" s="45"/>
-      <c r="AI14" s="46"/>
-      <c r="AJ14" s="45">
+      <c r="AH14" s="40"/>
+      <c r="AI14" s="41"/>
+      <c r="AJ14" s="40">
         <f>AVERAGE(AJ4:AJ13)</f>
         <v>0</v>
       </c>
-      <c r="AK14" s="45"/>
-      <c r="AL14" s="46"/>
-      <c r="AM14" s="45">
+      <c r="AK14" s="40"/>
+      <c r="AL14" s="41"/>
+      <c r="AM14" s="40">
         <f>AVERAGE(AM4:AM13)</f>
         <v>0</v>
       </c>
-      <c r="AN14" s="45"/>
-      <c r="AO14" s="46"/>
-      <c r="AP14" s="45">
+      <c r="AN14" s="40"/>
+      <c r="AO14" s="41"/>
+      <c r="AP14" s="40">
         <f>AVERAGE(AP4:AP13)</f>
         <v>0</v>
       </c>
-      <c r="AQ14" s="45"/>
-      <c r="AR14" s="46"/>
+      <c r="AQ14" s="40"/>
+      <c r="AR14" s="41"/>
     </row>
     <row r="15" spans="1:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B15" s="6"/>
@@ -4841,19 +4841,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="AM14:AO14"/>
-    <mergeCell ref="X14:Z14"/>
-    <mergeCell ref="AA14:AC14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AG14:AI14"/>
-    <mergeCell ref="AJ14:AL14"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:Q14"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AP14:AR14"/>
@@ -4870,6 +4857,19 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="AM14:AO14"/>
+    <mergeCell ref="X14:Z14"/>
+    <mergeCell ref="AA14:AC14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AG14:AI14"/>
+    <mergeCell ref="AJ14:AL14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
